--- a/modelo_clientes_v2.xlsx
+++ b/modelo_clientes_v2.xlsx
@@ -2262,11 +2262,11 @@
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <_dlc_DocId xmlns="4d331076-a25e-4ded-92a5-68080adce84b">NU5SJ7MYYK4T-382434567-77375</_dlc_DocId>
+    <_dlc_DocId xmlns="4d331076-a25e-4ded-92a5-68080adce84b">NU5SJ7MYYK4T-382434567-77483</_dlc_DocId>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <_dlc_DocIdUrl xmlns="4d331076-a25e-4ded-92a5-68080adce84b">
-      <Url>https://blocktimeit.sharepoint.com/sites/TEC/_layouts/15/DocIdRedir.aspx?ID=NU5SJ7MYYK4T-382434567-77375</Url>
-      <Description>NU5SJ7MYYK4T-382434567-77375</Description>
+      <Url>https://blocktimeit.sharepoint.com/sites/TEC/_layouts/15/DocIdRedir.aspx?ID=NU5SJ7MYYK4T-382434567-77483</Url>
+      <Description>NU5SJ7MYYK4T-382434567-77483</Description>
     </_dlc_DocIdUrl>
     <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="3686c4e4-beae-4105-a017-7572a71c63b6">
